--- a/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
@@ -442,37 +442,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="C1" s="1">
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="D1" s="1">
-        <v>46092</v>
+        <v>46113</v>
       </c>
       <c r="E1" s="1">
-        <v>46099</v>
+        <v>46120</v>
       </c>
       <c r="F1" s="1">
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="G1" s="1">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="H1" s="1">
-        <v>46120</v>
+        <v>46141</v>
       </c>
       <c r="I1" s="1">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="J1" s="1">
-        <v>46134</v>
+        <v>46155</v>
       </c>
       <c r="K1" s="1">
-        <v>46141</v>
+        <v>46162</v>
       </c>
       <c r="L1" s="1">
-        <v>46148</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -480,37 +480,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>47.7</v>
+        <v>55.6</v>
       </c>
       <c r="C2">
-        <v>47.6</v>
+        <v>61.4</v>
       </c>
       <c r="D2">
-        <v>47.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E2">
-        <v>48.2</v>
+        <v>78</v>
       </c>
       <c r="F2">
-        <v>48.8</v>
+        <v>88.3</v>
       </c>
       <c r="G2">
-        <v>49.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H2">
-        <v>50.2</v>
+        <v>111.2</v>
       </c>
       <c r="I2">
-        <v>51</v>
+        <v>122.7</v>
       </c>
       <c r="J2">
-        <v>51.8</v>
+        <v>133.3</v>
       </c>
       <c r="K2">
-        <v>52.7</v>
+        <v>142.4</v>
       </c>
       <c r="L2">
-        <v>53.5</v>
+        <v>149.6</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -518,37 +518,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>67.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="C3">
-        <v>71.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D3">
-        <v>75.8</v>
+        <v>102.9</v>
       </c>
       <c r="E3">
-        <v>80.2</v>
+        <v>112.5</v>
       </c>
       <c r="F3">
-        <v>84.8</v>
+        <v>122.4</v>
       </c>
       <c r="G3">
-        <v>89.2</v>
+        <v>132</v>
       </c>
       <c r="H3">
-        <v>93.2</v>
+        <v>141</v>
       </c>
       <c r="I3">
-        <v>96.7</v>
+        <v>148.7</v>
       </c>
       <c r="J3">
-        <v>99.40000000000001</v>
+        <v>154.9</v>
       </c>
       <c r="K3">
-        <v>101.3</v>
+        <v>159.2</v>
       </c>
       <c r="L3">
-        <v>102.2</v>
+        <v>161.2</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -556,37 +556,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>30.7</v>
+        <v>36.4</v>
       </c>
       <c r="C4">
-        <v>29.1</v>
+        <v>42.8</v>
       </c>
       <c r="D4">
-        <v>28.2</v>
+        <v>51.5</v>
       </c>
       <c r="E4">
-        <v>28.2</v>
+        <v>62.3</v>
       </c>
       <c r="F4">
-        <v>28.9</v>
+        <v>74.8</v>
       </c>
       <c r="G4">
-        <v>30.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H4">
-        <v>32.3</v>
+        <v>102.5</v>
       </c>
       <c r="I4">
-        <v>34.8</v>
+        <v>116.4</v>
       </c>
       <c r="J4">
-        <v>37.6</v>
+        <v>129.3</v>
       </c>
       <c r="K4">
-        <v>40.6</v>
+        <v>140.5</v>
       </c>
       <c r="L4">
-        <v>43.6</v>
+        <v>149.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -594,37 +594,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>56.4</v>
+        <v>59.8</v>
       </c>
       <c r="C5">
-        <v>56.4</v>
+        <v>62.2</v>
       </c>
       <c r="D5">
-        <v>56.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E5">
-        <v>56.3</v>
+        <v>68.5</v>
       </c>
       <c r="F5">
-        <v>56</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G5">
-        <v>55.7</v>
+        <v>76.5</v>
       </c>
       <c r="H5">
-        <v>55</v>
+        <v>80.7</v>
       </c>
       <c r="I5">
-        <v>54.2</v>
+        <v>84.8</v>
       </c>
       <c r="J5">
-        <v>53.3</v>
+        <v>88.7</v>
       </c>
       <c r="K5">
-        <v>52.2</v>
+        <v>92</v>
       </c>
       <c r="L5">
-        <v>51.2</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -632,37 +632,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>48.1</v>
+        <v>60.1</v>
       </c>
       <c r="C6">
-        <v>48.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>76.7</v>
       </c>
       <c r="E6">
-        <v>48.8</v>
+        <v>87.8</v>
       </c>
       <c r="F6">
-        <v>48.2</v>
+        <v>100.6</v>
       </c>
       <c r="G6">
-        <v>47.1</v>
+        <v>114.7</v>
       </c>
       <c r="H6">
-        <v>45.7</v>
+        <v>129.5</v>
       </c>
       <c r="I6">
-        <v>44.2</v>
+        <v>144.3</v>
       </c>
       <c r="J6">
-        <v>42.7</v>
+        <v>158.4</v>
       </c>
       <c r="K6">
-        <v>41.4</v>
+        <v>170.7</v>
       </c>
       <c r="L6">
-        <v>40.5</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -670,37 +670,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>38.2</v>
+        <v>53.6</v>
       </c>
       <c r="C7">
-        <v>39.1</v>
+        <v>63.7</v>
       </c>
       <c r="D7">
-        <v>39.8</v>
+        <v>76.7</v>
       </c>
       <c r="E7">
-        <v>40.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F7">
-        <v>40.7</v>
+        <v>110.8</v>
       </c>
       <c r="G7">
-        <v>41</v>
+        <v>131.1</v>
       </c>
       <c r="H7">
-        <v>41.3</v>
+        <v>152.6</v>
       </c>
       <c r="I7">
-        <v>41.9</v>
+        <v>174.2</v>
       </c>
       <c r="J7">
-        <v>42.9</v>
+        <v>194.7</v>
       </c>
       <c r="K7">
-        <v>44.3</v>
+        <v>212.7</v>
       </c>
       <c r="L7">
-        <v>46.1</v>
+        <v>227.1</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -708,37 +708,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>58.9</v>
+        <v>67</v>
       </c>
       <c r="C8">
-        <v>58.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D8">
-        <v>58.2</v>
+        <v>81</v>
       </c>
       <c r="E8">
-        <v>58.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F8">
-        <v>58.2</v>
+        <v>101.4</v>
       </c>
       <c r="G8">
-        <v>58.3</v>
+        <v>113</v>
       </c>
       <c r="H8">
-        <v>58.4</v>
+        <v>125</v>
       </c>
       <c r="I8">
-        <v>58.5</v>
+        <v>136.6</v>
       </c>
       <c r="J8">
-        <v>58.6</v>
+        <v>147.2</v>
       </c>
       <c r="K8">
-        <v>58.7</v>
+        <v>156.1</v>
       </c>
       <c r="L8">
-        <v>58.7</v>
+        <v>162.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -746,37 +746,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>44.6</v>
+        <v>50.1</v>
       </c>
       <c r="C9">
-        <v>44</v>
+        <v>55.4</v>
       </c>
       <c r="D9">
-        <v>43.4</v>
+        <v>62.4</v>
       </c>
       <c r="E9">
-        <v>42.8</v>
+        <v>71.3</v>
       </c>
       <c r="F9">
-        <v>41.9</v>
+        <v>81.8</v>
       </c>
       <c r="G9">
-        <v>41</v>
+        <v>93.7</v>
       </c>
       <c r="H9">
-        <v>39.8</v>
+        <v>106.6</v>
       </c>
       <c r="I9">
-        <v>38.7</v>
+        <v>119.9</v>
       </c>
       <c r="J9">
-        <v>37.6</v>
+        <v>132.8</v>
       </c>
       <c r="K9">
-        <v>36.8</v>
+        <v>144.8</v>
       </c>
       <c r="L9">
-        <v>36.2</v>
+        <v>154.9</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -784,37 +784,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>46.8</v>
+        <v>43.6</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>44.1</v>
       </c>
       <c r="D10">
-        <v>43.8</v>
+        <v>45.4</v>
       </c>
       <c r="E10">
-        <v>43.1</v>
+        <v>47.4</v>
       </c>
       <c r="F10">
-        <v>42.8</v>
+        <v>49.9</v>
       </c>
       <c r="G10">
-        <v>43</v>
+        <v>52.8</v>
       </c>
       <c r="H10">
-        <v>43.5</v>
+        <v>55.9</v>
       </c>
       <c r="I10">
-        <v>44.2</v>
+        <v>59.1</v>
       </c>
       <c r="J10">
-        <v>44.9</v>
+        <v>62.2</v>
       </c>
       <c r="K10">
-        <v>45.6</v>
+        <v>65</v>
       </c>
       <c r="L10">
-        <v>46.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -822,37 +822,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>60.4</v>
+        <v>61.7</v>
       </c>
       <c r="C11">
-        <v>60</v>
+        <v>63.3</v>
       </c>
       <c r="D11">
-        <v>59.7</v>
+        <v>65.5</v>
       </c>
       <c r="E11">
-        <v>59.2</v>
+        <v>68.2</v>
       </c>
       <c r="F11">
-        <v>58.5</v>
+        <v>71.5</v>
       </c>
       <c r="G11">
-        <v>57.5</v>
+        <v>75.2</v>
       </c>
       <c r="H11">
-        <v>56.3</v>
+        <v>79.2</v>
       </c>
       <c r="I11">
-        <v>54.9</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="J11">
-        <v>53.4</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K11">
-        <v>51.8</v>
+        <v>91.5</v>
       </c>
       <c r="L11">
-        <v>50.3</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -860,37 +860,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>62.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C12">
-        <v>64</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D12">
-        <v>65.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="E12">
-        <v>67.5</v>
+        <v>95</v>
       </c>
       <c r="F12">
-        <v>69.59999999999999</v>
+        <v>104.7</v>
       </c>
       <c r="G12">
-        <v>71.7</v>
+        <v>114.9</v>
       </c>
       <c r="H12">
-        <v>73.7</v>
+        <v>125.1</v>
       </c>
       <c r="I12">
-        <v>75.40000000000001</v>
+        <v>134.9</v>
       </c>
       <c r="J12">
-        <v>76.8</v>
+        <v>143.6</v>
       </c>
       <c r="K12">
-        <v>77.59999999999999</v>
+        <v>150.8</v>
       </c>
       <c r="L12">
-        <v>77.90000000000001</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -898,37 +898,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>63.4</v>
+        <v>81</v>
       </c>
       <c r="C13">
-        <v>65.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D13">
-        <v>67.90000000000001</v>
+        <v>102.6</v>
       </c>
       <c r="E13">
-        <v>70.90000000000001</v>
+        <v>115.7</v>
       </c>
       <c r="F13">
-        <v>74.09999999999999</v>
+        <v>129.8</v>
       </c>
       <c r="G13">
-        <v>77.40000000000001</v>
+        <v>144.1</v>
       </c>
       <c r="H13">
-        <v>80.59999999999999</v>
+        <v>157.9</v>
       </c>
       <c r="I13">
-        <v>83.5</v>
+        <v>170.5</v>
       </c>
       <c r="J13">
-        <v>85.8</v>
+        <v>181.1</v>
       </c>
       <c r="K13">
-        <v>87.5</v>
+        <v>189.1</v>
       </c>
       <c r="L13">
-        <v>88.5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -936,37 +936,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>29.6</v>
+        <v>33.4</v>
       </c>
       <c r="C14">
-        <v>29.1</v>
+        <v>37.5</v>
       </c>
       <c r="D14">
-        <v>28.9</v>
+        <v>43.1</v>
       </c>
       <c r="E14">
-        <v>29.2</v>
+        <v>50.2</v>
       </c>
       <c r="F14">
-        <v>29.8</v>
+        <v>58.6</v>
       </c>
       <c r="G14">
-        <v>30.8</v>
+        <v>68</v>
       </c>
       <c r="H14">
-        <v>32.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I14">
-        <v>33.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J14">
-        <v>35.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K14">
-        <v>37.8</v>
+        <v>105.9</v>
       </c>
       <c r="L14">
-        <v>39.8</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -974,37 +974,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>28.8</v>
+        <v>36.7</v>
       </c>
       <c r="C15">
-        <v>27.6</v>
+        <v>43.9</v>
       </c>
       <c r="D15">
-        <v>27.2</v>
+        <v>53.5</v>
       </c>
       <c r="E15">
-        <v>27.6</v>
+        <v>65.2</v>
       </c>
       <c r="F15">
-        <v>28.5</v>
+        <v>78.5</v>
       </c>
       <c r="G15">
-        <v>30</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H15">
-        <v>31.9</v>
+        <v>107.7</v>
       </c>
       <c r="I15">
-        <v>34.1</v>
+        <v>122.1</v>
       </c>
       <c r="J15">
-        <v>36.5</v>
+        <v>135.4</v>
       </c>
       <c r="K15">
-        <v>38.9</v>
+        <v>146.9</v>
       </c>
       <c r="L15">
-        <v>41.3</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1012,37 +1012,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>48.7</v>
+        <v>61.4</v>
       </c>
       <c r="C16">
-        <v>49.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D16">
-        <v>50</v>
+        <v>79.8</v>
       </c>
       <c r="E16">
-        <v>51.5</v>
+        <v>91.8</v>
       </c>
       <c r="F16">
-        <v>53.5</v>
+        <v>105.1</v>
       </c>
       <c r="G16">
-        <v>55.9</v>
+        <v>119.2</v>
       </c>
       <c r="H16">
-        <v>58.6</v>
+        <v>133.3</v>
       </c>
       <c r="I16">
-        <v>61.6</v>
+        <v>146.8</v>
       </c>
       <c r="J16">
-        <v>64.59999999999999</v>
+        <v>158.8</v>
       </c>
       <c r="K16">
-        <v>67.59999999999999</v>
+        <v>168.6</v>
       </c>
       <c r="L16">
-        <v>70.40000000000001</v>
+        <v>175.7</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1050,37 +1050,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>52.8</v>
+        <v>66</v>
       </c>
       <c r="C17">
-        <v>53.1</v>
+        <v>74.7</v>
       </c>
       <c r="D17">
-        <v>53.9</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E17">
-        <v>54.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F17">
-        <v>56.3</v>
+        <v>112.8</v>
       </c>
       <c r="G17">
-        <v>57.9</v>
+        <v>128</v>
       </c>
       <c r="H17">
-        <v>59.7</v>
+        <v>143.4</v>
       </c>
       <c r="I17">
-        <v>61.6</v>
+        <v>158.1</v>
       </c>
       <c r="J17">
-        <v>63.4</v>
+        <v>171.3</v>
       </c>
       <c r="K17">
-        <v>65.2</v>
+        <v>182.1</v>
       </c>
       <c r="L17">
-        <v>66.8</v>
+        <v>189.9</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1088,37 +1088,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="C18">
-        <v>48.9</v>
+        <v>53.7</v>
       </c>
       <c r="D18">
-        <v>47</v>
+        <v>58.3</v>
       </c>
       <c r="E18">
-        <v>44.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F18">
-        <v>42.6</v>
+        <v>72.7</v>
       </c>
       <c r="G18">
-        <v>40.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H18">
-        <v>37.9</v>
+        <v>93.2</v>
       </c>
       <c r="I18">
-        <v>35.7</v>
+        <v>104.8</v>
       </c>
       <c r="J18">
-        <v>33.9</v>
+        <v>116.4</v>
       </c>
       <c r="K18">
-        <v>32.5</v>
+        <v>127.3</v>
       </c>
       <c r="L18">
-        <v>31.7</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1126,37 +1126,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>40.3</v>
+        <v>49.5</v>
       </c>
       <c r="C19">
-        <v>40.4</v>
+        <v>56</v>
       </c>
       <c r="D19">
-        <v>40.6</v>
+        <v>64.5</v>
       </c>
       <c r="E19">
-        <v>40.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G19">
-        <v>41.3</v>
+        <v>100.3</v>
       </c>
       <c r="H19">
-        <v>41.7</v>
+        <v>114.4</v>
       </c>
       <c r="I19">
-        <v>42.4</v>
+        <v>128.4</v>
       </c>
       <c r="J19">
-        <v>43.3</v>
+        <v>141.6</v>
       </c>
       <c r="K19">
-        <v>44.3</v>
+        <v>153.2</v>
       </c>
       <c r="L19">
-        <v>45.6</v>
+        <v>162.4</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1164,37 +1164,37 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>40.7</v>
+        <v>44.5</v>
       </c>
       <c r="C20">
-        <v>40</v>
+        <v>48.3</v>
       </c>
       <c r="D20">
-        <v>39.3</v>
+        <v>53.5</v>
       </c>
       <c r="E20">
-        <v>38.4</v>
+        <v>60.1</v>
       </c>
       <c r="F20">
-        <v>37.6</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G20">
-        <v>36.7</v>
+        <v>77.3</v>
       </c>
       <c r="H20">
-        <v>35.8</v>
+        <v>87.2</v>
       </c>
       <c r="I20">
-        <v>35.1</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="J20">
-        <v>34.5</v>
+        <v>107.3</v>
       </c>
       <c r="K20">
-        <v>34.3</v>
+        <v>116.4</v>
       </c>
       <c r="L20">
-        <v>34.4</v>
+        <v>124.2</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1202,37 +1202,37 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>36.8</v>
+        <v>41.9</v>
       </c>
       <c r="C21">
-        <v>35.2</v>
+        <v>47.4</v>
       </c>
       <c r="D21">
-        <v>34.2</v>
+        <v>55</v>
       </c>
       <c r="E21">
-        <v>33.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F21">
-        <v>33.9</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G21">
-        <v>34.6</v>
+        <v>87.5</v>
       </c>
       <c r="H21">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="I21">
-        <v>37.8</v>
+        <v>112.3</v>
       </c>
       <c r="J21">
-        <v>40</v>
+        <v>123.7</v>
       </c>
       <c r="K21">
-        <v>42.4</v>
+        <v>133.6</v>
       </c>
       <c r="L21">
-        <v>44.9</v>
+        <v>141.3</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
@@ -442,37 +442,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46099</v>
+        <v>46134</v>
       </c>
       <c r="C1" s="1">
-        <v>46106</v>
+        <v>46141</v>
       </c>
       <c r="D1" s="1">
-        <v>46113</v>
+        <v>46148</v>
       </c>
       <c r="E1" s="1">
-        <v>46120</v>
+        <v>46155</v>
       </c>
       <c r="F1" s="1">
-        <v>46127</v>
+        <v>46162</v>
       </c>
       <c r="G1" s="1">
-        <v>46134</v>
+        <v>46169</v>
       </c>
       <c r="H1" s="1">
-        <v>46141</v>
+        <v>46176</v>
       </c>
       <c r="I1" s="1">
-        <v>46148</v>
+        <v>46183</v>
       </c>
       <c r="J1" s="1">
-        <v>46155</v>
+        <v>46190</v>
       </c>
       <c r="K1" s="1">
-        <v>46162</v>
+        <v>46197</v>
       </c>
       <c r="L1" s="1">
-        <v>46169</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -480,37 +480,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>55.6</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C2">
-        <v>61.4</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D2">
-        <v>68.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="E2">
-        <v>78</v>
+        <v>84.5</v>
       </c>
       <c r="F2">
-        <v>88.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G2">
-        <v>99.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="H2">
-        <v>111.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I2">
-        <v>122.7</v>
+        <v>61.1</v>
       </c>
       <c r="J2">
-        <v>133.3</v>
+        <v>51.6</v>
       </c>
       <c r="K2">
-        <v>142.4</v>
+        <v>41.8</v>
       </c>
       <c r="L2">
-        <v>149.6</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -518,37 +518,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>85.59999999999999</v>
+        <v>112.4</v>
       </c>
       <c r="C3">
-        <v>93.8</v>
+        <v>113.1</v>
       </c>
       <c r="D3">
-        <v>102.9</v>
+        <v>111.6</v>
       </c>
       <c r="E3">
-        <v>112.5</v>
+        <v>107.7</v>
       </c>
       <c r="F3">
-        <v>122.4</v>
+        <v>101.7</v>
       </c>
       <c r="G3">
-        <v>132</v>
+        <v>93.7</v>
       </c>
       <c r="H3">
-        <v>141</v>
+        <v>84.2</v>
       </c>
       <c r="I3">
-        <v>148.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J3">
-        <v>154.9</v>
+        <v>63.3</v>
       </c>
       <c r="K3">
-        <v>159.2</v>
+        <v>53.2</v>
       </c>
       <c r="L3">
-        <v>161.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -556,37 +556,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>36.4</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C4">
-        <v>42.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D4">
-        <v>51.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E4">
-        <v>62.3</v>
+        <v>74.2</v>
       </c>
       <c r="F4">
-        <v>74.8</v>
+        <v>71</v>
       </c>
       <c r="G4">
-        <v>88.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="H4">
-        <v>102.5</v>
+        <v>56.9</v>
       </c>
       <c r="I4">
-        <v>116.4</v>
+        <v>46.7</v>
       </c>
       <c r="J4">
-        <v>129.3</v>
+        <v>35.3</v>
       </c>
       <c r="K4">
-        <v>140.5</v>
+        <v>23.5</v>
       </c>
       <c r="L4">
-        <v>149.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -594,37 +594,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>59.8</v>
+        <v>75</v>
       </c>
       <c r="C5">
-        <v>62.2</v>
+        <v>77.7</v>
       </c>
       <c r="D5">
-        <v>65.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E5">
-        <v>68.5</v>
+        <v>81.2</v>
       </c>
       <c r="F5">
-        <v>72.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="G5">
-        <v>76.5</v>
+        <v>80.7</v>
       </c>
       <c r="H5">
-        <v>80.7</v>
+        <v>78.8</v>
       </c>
       <c r="I5">
-        <v>84.8</v>
+        <v>75.8</v>
       </c>
       <c r="J5">
-        <v>88.7</v>
+        <v>71.8</v>
       </c>
       <c r="K5">
-        <v>92</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L5">
-        <v>94.7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -632,37 +632,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>60.1</v>
+        <v>91.7</v>
       </c>
       <c r="C6">
-        <v>67.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D6">
-        <v>76.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E6">
-        <v>87.8</v>
+        <v>96.7</v>
       </c>
       <c r="F6">
-        <v>100.6</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G6">
-        <v>114.7</v>
+        <v>86.7</v>
       </c>
       <c r="H6">
-        <v>129.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I6">
-        <v>144.3</v>
+        <v>66.2</v>
       </c>
       <c r="J6">
-        <v>158.4</v>
+        <v>53.3</v>
       </c>
       <c r="K6">
-        <v>170.7</v>
+        <v>39.6</v>
       </c>
       <c r="L6">
-        <v>180.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -670,37 +670,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>53.6</v>
+        <v>89.3</v>
       </c>
       <c r="C7">
-        <v>63.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D7">
-        <v>76.7</v>
+        <v>94.3</v>
       </c>
       <c r="E7">
-        <v>92.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="F7">
-        <v>110.8</v>
+        <v>87.5</v>
       </c>
       <c r="G7">
-        <v>131.1</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H7">
-        <v>152.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I7">
-        <v>174.2</v>
+        <v>55.1</v>
       </c>
       <c r="J7">
-        <v>194.7</v>
+        <v>40.5</v>
       </c>
       <c r="K7">
-        <v>212.7</v>
+        <v>25.5</v>
       </c>
       <c r="L7">
-        <v>227.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -708,37 +708,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>67</v>
+        <v>91.2</v>
       </c>
       <c r="C8">
-        <v>73.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="D8">
-        <v>81</v>
+        <v>94.5</v>
       </c>
       <c r="E8">
-        <v>90.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="F8">
-        <v>101.4</v>
+        <v>89.8</v>
       </c>
       <c r="G8">
-        <v>113</v>
+        <v>84.3</v>
       </c>
       <c r="H8">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="I8">
-        <v>136.6</v>
+        <v>68.2</v>
       </c>
       <c r="J8">
-        <v>147.2</v>
+        <v>58.7</v>
       </c>
       <c r="K8">
-        <v>156.1</v>
+        <v>48.9</v>
       </c>
       <c r="L8">
-        <v>162.7</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -746,37 +746,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>50.1</v>
+        <v>73.7</v>
       </c>
       <c r="C9">
-        <v>55.4</v>
+        <v>76.5</v>
       </c>
       <c r="D9">
-        <v>62.4</v>
+        <v>77.7</v>
       </c>
       <c r="E9">
-        <v>71.3</v>
+        <v>77</v>
       </c>
       <c r="F9">
-        <v>81.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G9">
-        <v>93.7</v>
+        <v>69</v>
       </c>
       <c r="H9">
-        <v>106.6</v>
+        <v>62</v>
       </c>
       <c r="I9">
-        <v>119.9</v>
+        <v>53.3</v>
       </c>
       <c r="J9">
-        <v>132.8</v>
+        <v>43.5</v>
       </c>
       <c r="K9">
-        <v>144.8</v>
+        <v>33.2</v>
       </c>
       <c r="L9">
-        <v>154.9</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -784,37 +784,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>43.6</v>
+        <v>53.3</v>
       </c>
       <c r="C10">
-        <v>44.1</v>
+        <v>55.3</v>
       </c>
       <c r="D10">
+        <v>56.8</v>
+      </c>
+      <c r="E10">
+        <v>57.5</v>
+      </c>
+      <c r="F10">
+        <v>57.4</v>
+      </c>
+      <c r="G10">
+        <v>56.4</v>
+      </c>
+      <c r="H10">
+        <v>54.6</v>
+      </c>
+      <c r="I10">
+        <v>52</v>
+      </c>
+      <c r="J10">
+        <v>48.9</v>
+      </c>
+      <c r="K10">
         <v>45.4</v>
       </c>
-      <c r="E10">
-        <v>47.4</v>
-      </c>
-      <c r="F10">
-        <v>49.9</v>
-      </c>
-      <c r="G10">
-        <v>52.8</v>
-      </c>
-      <c r="H10">
-        <v>55.9</v>
-      </c>
-      <c r="I10">
-        <v>59.1</v>
-      </c>
-      <c r="J10">
-        <v>62.2</v>
-      </c>
-      <c r="K10">
-        <v>65</v>
-      </c>
       <c r="L10">
-        <v>67.40000000000001</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -822,37 +822,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>61.7</v>
+        <v>73.7</v>
       </c>
       <c r="C11">
-        <v>63.3</v>
+        <v>75.3</v>
       </c>
       <c r="D11">
-        <v>65.5</v>
+        <v>76.2</v>
       </c>
       <c r="E11">
-        <v>68.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F11">
-        <v>71.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G11">
-        <v>75.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H11">
-        <v>79.2</v>
+        <v>68.8</v>
       </c>
       <c r="I11">
-        <v>83.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J11">
-        <v>87.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="K11">
-        <v>91.5</v>
+        <v>52.5</v>
       </c>
       <c r="L11">
-        <v>94.8</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -860,37 +860,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>72.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="C12">
-        <v>78.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D12">
-        <v>86.2</v>
+        <v>95.2</v>
       </c>
       <c r="E12">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="F12">
-        <v>104.7</v>
+        <v>88.2</v>
       </c>
       <c r="G12">
-        <v>114.9</v>
+        <v>81.8</v>
       </c>
       <c r="H12">
-        <v>125.1</v>
+        <v>74</v>
       </c>
       <c r="I12">
-        <v>134.9</v>
+        <v>65</v>
       </c>
       <c r="J12">
-        <v>143.6</v>
+        <v>55.5</v>
       </c>
       <c r="K12">
-        <v>150.8</v>
+        <v>46.1</v>
       </c>
       <c r="L12">
-        <v>156</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -898,37 +898,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>81</v>
+        <v>112.9</v>
       </c>
       <c r="C13">
-        <v>90.90000000000001</v>
+        <v>114.2</v>
       </c>
       <c r="D13">
-        <v>102.6</v>
+        <v>112.5</v>
       </c>
       <c r="E13">
-        <v>115.7</v>
+        <v>107.8</v>
       </c>
       <c r="F13">
-        <v>129.8</v>
+        <v>100.3</v>
       </c>
       <c r="G13">
-        <v>144.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H13">
-        <v>157.9</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I13">
-        <v>170.5</v>
+        <v>64.8</v>
       </c>
       <c r="J13">
-        <v>181.1</v>
+        <v>51.3</v>
       </c>
       <c r="K13">
-        <v>189.1</v>
+        <v>38.3</v>
       </c>
       <c r="L13">
-        <v>194</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -936,37 +936,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>33.4</v>
+        <v>56.4</v>
       </c>
       <c r="C14">
-        <v>37.5</v>
+        <v>60.3</v>
       </c>
       <c r="D14">
-        <v>43.1</v>
+        <v>63.1</v>
       </c>
       <c r="E14">
-        <v>50.2</v>
+        <v>64.3</v>
       </c>
       <c r="F14">
-        <v>58.6</v>
+        <v>63.7</v>
       </c>
       <c r="G14">
-        <v>68</v>
+        <v>61.3</v>
       </c>
       <c r="H14">
-        <v>77.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="I14">
-        <v>87.90000000000001</v>
+        <v>51.4</v>
       </c>
       <c r="J14">
-        <v>97.40000000000001</v>
+        <v>44.5</v>
       </c>
       <c r="K14">
-        <v>105.9</v>
+        <v>37</v>
       </c>
       <c r="L14">
-        <v>113</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -974,37 +974,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>36.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C15">
-        <v>43.9</v>
+        <v>75.2</v>
       </c>
       <c r="D15">
-        <v>53.5</v>
+        <v>78.2</v>
       </c>
       <c r="E15">
-        <v>65.2</v>
+        <v>78.8</v>
       </c>
       <c r="F15">
-        <v>78.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G15">
-        <v>92.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H15">
-        <v>107.7</v>
+        <v>66</v>
       </c>
       <c r="I15">
-        <v>122.1</v>
+        <v>57.7</v>
       </c>
       <c r="J15">
-        <v>135.4</v>
+        <v>48.3</v>
       </c>
       <c r="K15">
-        <v>146.9</v>
+        <v>38.5</v>
       </c>
       <c r="L15">
-        <v>155.8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1012,37 +1012,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>61.4</v>
+        <v>93.5</v>
       </c>
       <c r="C16">
-        <v>69.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D16">
-        <v>79.8</v>
+        <v>99.2</v>
       </c>
       <c r="E16">
-        <v>91.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F16">
-        <v>105.1</v>
+        <v>95.7</v>
       </c>
       <c r="G16">
-        <v>119.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H16">
-        <v>133.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I16">
-        <v>146.8</v>
+        <v>74.2</v>
       </c>
       <c r="J16">
-        <v>158.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K16">
-        <v>168.6</v>
+        <v>54.3</v>
       </c>
       <c r="L16">
-        <v>175.7</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1050,37 +1050,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>66</v>
+        <v>95.8</v>
       </c>
       <c r="C17">
-        <v>74.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D17">
-        <v>85.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="E17">
-        <v>98.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="F17">
-        <v>112.8</v>
+        <v>88.3</v>
       </c>
       <c r="G17">
-        <v>128</v>
+        <v>79.7</v>
       </c>
       <c r="H17">
-        <v>143.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I17">
-        <v>158.1</v>
+        <v>57.1</v>
       </c>
       <c r="J17">
-        <v>171.3</v>
+        <v>44.4</v>
       </c>
       <c r="K17">
-        <v>182.1</v>
+        <v>32</v>
       </c>
       <c r="L17">
-        <v>189.9</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1088,37 +1088,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>50.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C18">
-        <v>53.7</v>
+        <v>75.8</v>
       </c>
       <c r="D18">
-        <v>58.3</v>
+        <v>79.2</v>
       </c>
       <c r="E18">
-        <v>64.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F18">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
       <c r="G18">
-        <v>82.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H18">
-        <v>93.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I18">
-        <v>104.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J18">
-        <v>116.4</v>
+        <v>64.7</v>
       </c>
       <c r="K18">
-        <v>127.3</v>
+        <v>56.6</v>
       </c>
       <c r="L18">
-        <v>137</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1126,37 +1126,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>49.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="C19">
-        <v>56</v>
+        <v>79.2</v>
       </c>
       <c r="D19">
-        <v>64.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E19">
-        <v>74.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F19">
-        <v>86.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G19">
-        <v>100.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H19">
-        <v>114.4</v>
+        <v>56.9</v>
       </c>
       <c r="I19">
-        <v>128.4</v>
+        <v>45.5</v>
       </c>
       <c r="J19">
-        <v>141.6</v>
+        <v>32.9</v>
       </c>
       <c r="K19">
-        <v>153.2</v>
+        <v>20</v>
       </c>
       <c r="L19">
-        <v>162.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1164,37 +1164,37 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>44.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C20">
-        <v>48.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D20">
-        <v>53.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E20">
-        <v>60.1</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F20">
-        <v>68.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G20">
-        <v>77.3</v>
+        <v>65.8</v>
       </c>
       <c r="H20">
-        <v>87.2</v>
+        <v>61</v>
       </c>
       <c r="I20">
-        <v>97.40000000000001</v>
+        <v>54.6</v>
       </c>
       <c r="J20">
-        <v>107.3</v>
+        <v>47</v>
       </c>
       <c r="K20">
-        <v>116.4</v>
+        <v>38.7</v>
       </c>
       <c r="L20">
-        <v>124.2</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1202,37 +1202,37 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>41.9</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C21">
-        <v>47.4</v>
+        <v>77.7</v>
       </c>
       <c r="D21">
-        <v>55</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E21">
-        <v>64.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F21">
-        <v>75.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="G21">
-        <v>87.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I21">
-        <v>112.3</v>
+        <v>63.7</v>
       </c>
       <c r="J21">
-        <v>123.7</v>
+        <v>54.3</v>
       </c>
       <c r="K21">
-        <v>133.6</v>
+        <v>44.2</v>
       </c>
       <c r="L21">
-        <v>141.3</v>
+        <v>34.1</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
@@ -442,37 +442,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="C1" s="1">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="D1" s="1">
-        <v>46148</v>
+        <v>46176</v>
       </c>
       <c r="E1" s="1">
-        <v>46155</v>
+        <v>46183</v>
       </c>
       <c r="F1" s="1">
-        <v>46162</v>
+        <v>46190</v>
       </c>
       <c r="G1" s="1">
-        <v>46169</v>
+        <v>46197</v>
       </c>
       <c r="H1" s="1">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="I1" s="1">
-        <v>46183</v>
+        <v>46211</v>
       </c>
       <c r="J1" s="1">
-        <v>46190</v>
+        <v>46218</v>
       </c>
       <c r="K1" s="1">
-        <v>46197</v>
+        <v>46225</v>
       </c>
       <c r="L1" s="1">
-        <v>46204</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -480,37 +480,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>80.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C2">
-        <v>83.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D2">
-        <v>85.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E2">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F2">
-        <v>81.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="G2">
-        <v>76.5</v>
+        <v>81</v>
       </c>
       <c r="H2">
-        <v>69.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I2">
-        <v>61.1</v>
+        <v>79.5</v>
       </c>
       <c r="J2">
-        <v>51.6</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K2">
-        <v>41.8</v>
+        <v>81</v>
       </c>
       <c r="L2">
-        <v>32.4</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -518,37 +518,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>112.4</v>
+        <v>108.5</v>
       </c>
       <c r="C3">
-        <v>113.1</v>
+        <v>104.5</v>
       </c>
       <c r="D3">
-        <v>111.6</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E3">
-        <v>107.7</v>
+        <v>95.3</v>
       </c>
       <c r="F3">
-        <v>101.7</v>
+        <v>91</v>
       </c>
       <c r="G3">
-        <v>93.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H3">
-        <v>84.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I3">
-        <v>73.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="J3">
-        <v>63.3</v>
+        <v>83.2</v>
       </c>
       <c r="K3">
-        <v>53.2</v>
+        <v>83.7</v>
       </c>
       <c r="L3">
-        <v>44</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -556,37 +556,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>68.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="C4">
-        <v>72.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="D4">
-        <v>74.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E4">
-        <v>74.2</v>
+        <v>72.8</v>
       </c>
       <c r="F4">
-        <v>71</v>
+        <v>69.7</v>
       </c>
       <c r="G4">
-        <v>65.2</v>
+        <v>66.8</v>
       </c>
       <c r="H4">
-        <v>56.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I4">
-        <v>46.7</v>
+        <v>63.5</v>
       </c>
       <c r="J4">
-        <v>35.3</v>
+        <v>63.5</v>
       </c>
       <c r="K4">
-        <v>23.5</v>
+        <v>64.7</v>
       </c>
       <c r="L4">
-        <v>12.2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -594,37 +594,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>75</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="C5">
-        <v>77.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D5">
-        <v>79.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="E5">
-        <v>81.2</v>
+        <v>81.7</v>
       </c>
       <c r="F5">
-        <v>81.5</v>
+        <v>81</v>
       </c>
       <c r="G5">
-        <v>80.7</v>
+        <v>80.2</v>
       </c>
       <c r="H5">
-        <v>78.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I5">
-        <v>75.8</v>
+        <v>78.7</v>
       </c>
       <c r="J5">
-        <v>71.8</v>
+        <v>78.2</v>
       </c>
       <c r="K5">
-        <v>67.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="L5">
-        <v>62</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -632,37 +632,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>91.7</v>
+        <v>100.8</v>
       </c>
       <c r="C6">
-        <v>95.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="D6">
-        <v>97.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="E6">
-        <v>96.7</v>
+        <v>92.5</v>
       </c>
       <c r="F6">
-        <v>93.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G6">
-        <v>86.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H6">
-        <v>77.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="I6">
-        <v>66.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J6">
-        <v>53.3</v>
+        <v>72.5</v>
       </c>
       <c r="K6">
-        <v>39.6</v>
+        <v>71.2</v>
       </c>
       <c r="L6">
-        <v>26.1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -670,37 +670,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>89.3</v>
+        <v>101.9</v>
       </c>
       <c r="C7">
-        <v>93.09999999999999</v>
+        <v>102.1</v>
       </c>
       <c r="D7">
-        <v>94.3</v>
+        <v>101.4</v>
       </c>
       <c r="E7">
-        <v>92.5</v>
+        <v>100.3</v>
       </c>
       <c r="F7">
-        <v>87.5</v>
+        <v>99</v>
       </c>
       <c r="G7">
-        <v>79.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="H7">
-        <v>68.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="I7">
-        <v>55.1</v>
+        <v>99.3</v>
       </c>
       <c r="J7">
-        <v>40.5</v>
+        <v>101.4</v>
       </c>
       <c r="K7">
-        <v>25.5</v>
+        <v>104.4</v>
       </c>
       <c r="L7">
-        <v>11.3</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -708,37 +708,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>91.2</v>
+        <v>95.5</v>
       </c>
       <c r="C8">
-        <v>93.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D8">
-        <v>94.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="E8">
-        <v>93.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F8">
-        <v>89.8</v>
+        <v>86.3</v>
       </c>
       <c r="G8">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="H8">
-        <v>77</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I8">
-        <v>68.2</v>
+        <v>81.8</v>
       </c>
       <c r="J8">
-        <v>58.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K8">
-        <v>48.9</v>
+        <v>83.3</v>
       </c>
       <c r="L8">
-        <v>39.7</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -746,37 +746,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>73.7</v>
+        <v>83.5</v>
       </c>
       <c r="C9">
-        <v>76.5</v>
+        <v>84</v>
       </c>
       <c r="D9">
-        <v>77.7</v>
+        <v>83.8</v>
       </c>
       <c r="E9">
-        <v>77</v>
+        <v>83.2</v>
       </c>
       <c r="F9">
-        <v>74.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G9">
-        <v>69</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H9">
-        <v>62</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I9">
-        <v>53.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="J9">
-        <v>43.5</v>
+        <v>81.8</v>
       </c>
       <c r="K9">
-        <v>33.2</v>
+        <v>83</v>
       </c>
       <c r="L9">
-        <v>23.1</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -784,37 +784,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>53.3</v>
+        <v>60.1</v>
       </c>
       <c r="C10">
-        <v>55.3</v>
+        <v>61.6</v>
       </c>
       <c r="D10">
-        <v>56.8</v>
+        <v>63.1</v>
       </c>
       <c r="E10">
-        <v>57.5</v>
+        <v>64.7</v>
       </c>
       <c r="F10">
-        <v>57.4</v>
+        <v>66.5</v>
       </c>
       <c r="G10">
-        <v>56.4</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H10">
-        <v>54.6</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I10">
-        <v>52</v>
+        <v>73.5</v>
       </c>
       <c r="J10">
-        <v>48.9</v>
+        <v>76.2</v>
       </c>
       <c r="K10">
-        <v>45.4</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L10">
-        <v>41.8</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -822,37 +822,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>73.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="C11">
-        <v>75.3</v>
+        <v>77.8</v>
       </c>
       <c r="D11">
-        <v>76.2</v>
+        <v>77.7</v>
       </c>
       <c r="E11">
-        <v>76.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="F11">
-        <v>74.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="G11">
-        <v>72.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="H11">
-        <v>68.8</v>
+        <v>77.3</v>
       </c>
       <c r="I11">
-        <v>64.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J11">
-        <v>58.6</v>
+        <v>78.3</v>
       </c>
       <c r="K11">
-        <v>52.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L11">
-        <v>46.2</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -860,37 +860,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>94.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C12">
-        <v>95.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D12">
-        <v>95.2</v>
+        <v>86</v>
       </c>
       <c r="E12">
-        <v>92.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F12">
-        <v>88.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G12">
-        <v>81.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H12">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="I12">
-        <v>65</v>
+        <v>74.2</v>
       </c>
       <c r="J12">
-        <v>55.5</v>
+        <v>74.8</v>
       </c>
       <c r="K12">
-        <v>46.1</v>
+        <v>76.3</v>
       </c>
       <c r="L12">
-        <v>37.4</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -898,37 +898,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>112.9</v>
+        <v>110.8</v>
       </c>
       <c r="C13">
-        <v>114.2</v>
+        <v>106.9</v>
       </c>
       <c r="D13">
-        <v>112.5</v>
+        <v>102.6</v>
       </c>
       <c r="E13">
-        <v>107.8</v>
+        <v>98.5</v>
       </c>
       <c r="F13">
-        <v>100.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G13">
-        <v>90.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H13">
-        <v>78.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="I13">
-        <v>64.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J13">
-        <v>51.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="K13">
-        <v>38.3</v>
+        <v>98.7</v>
       </c>
       <c r="L13">
-        <v>26.8</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -936,37 +936,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>56.4</v>
+        <v>68</v>
       </c>
       <c r="C14">
-        <v>60.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D14">
-        <v>63.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E14">
-        <v>64.3</v>
+        <v>67.5</v>
       </c>
       <c r="F14">
+        <v>66.2</v>
+      </c>
+      <c r="G14">
+        <v>64.8</v>
+      </c>
+      <c r="H14">
         <v>63.7</v>
       </c>
-      <c r="G14">
-        <v>61.3</v>
-      </c>
-      <c r="H14">
-        <v>57.1</v>
-      </c>
       <c r="I14">
-        <v>51.4</v>
+        <v>62.9</v>
       </c>
       <c r="J14">
-        <v>44.5</v>
+        <v>62.7</v>
       </c>
       <c r="K14">
-        <v>37</v>
+        <v>63.2</v>
       </c>
       <c r="L14">
-        <v>29.4</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -974,37 +974,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>70.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="C15">
-        <v>75.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D15">
-        <v>78.2</v>
+        <v>85.3</v>
       </c>
       <c r="E15">
-        <v>78.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F15">
-        <v>76.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G15">
-        <v>72.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="H15">
-        <v>66</v>
+        <v>81.7</v>
       </c>
       <c r="I15">
-        <v>57.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="J15">
-        <v>48.3</v>
+        <v>82.8</v>
       </c>
       <c r="K15">
-        <v>38.5</v>
+        <v>84.3</v>
       </c>
       <c r="L15">
-        <v>29</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1012,37 +1012,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>93.5</v>
+        <v>101.6</v>
       </c>
       <c r="C16">
-        <v>97.40000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D16">
-        <v>99.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="E16">
-        <v>98.59999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F16">
-        <v>95.7</v>
+        <v>89.8</v>
       </c>
       <c r="G16">
-        <v>90.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H16">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="I16">
-        <v>74.2</v>
+        <v>80.8</v>
       </c>
       <c r="J16">
-        <v>64.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K16">
-        <v>54.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L16">
-        <v>44.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1050,37 +1050,37 @@
         <v>15</v>
       </c>
       <c r="B17">
+        <v>98.2</v>
+      </c>
+      <c r="C17">
         <v>95.8</v>
       </c>
-      <c r="C17">
-        <v>97.90000000000001</v>
-      </c>
       <c r="D17">
-        <v>97.5</v>
+        <v>92.8</v>
       </c>
       <c r="E17">
-        <v>94.3</v>
+        <v>89.7</v>
       </c>
       <c r="F17">
-        <v>88.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G17">
-        <v>79.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H17">
-        <v>69.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="I17">
-        <v>57.1</v>
+        <v>86</v>
       </c>
       <c r="J17">
-        <v>44.4</v>
+        <v>88.2</v>
       </c>
       <c r="K17">
-        <v>32</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="L17">
-        <v>20.8</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1088,37 +1088,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>71.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="C18">
-        <v>75.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D18">
-        <v>79.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="E18">
-        <v>81.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="F18">
-        <v>81.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G18">
-        <v>80.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="H18">
-        <v>76.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I18">
-        <v>71.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="J18">
-        <v>64.7</v>
+        <v>78.5</v>
       </c>
       <c r="K18">
-        <v>56.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L18">
-        <v>48.1</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1126,37 +1126,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>76.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C19">
-        <v>79.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D19">
-        <v>79.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E19">
-        <v>78.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F19">
-        <v>73.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="G19">
-        <v>66.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H19">
-        <v>56.9</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I19">
-        <v>45.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="J19">
-        <v>32.9</v>
+        <v>84</v>
       </c>
       <c r="K19">
-        <v>20</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L19">
-        <v>7.7</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1164,37 +1164,37 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>64.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="C20">
-        <v>67.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D20">
-        <v>69.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E20">
-        <v>70.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="F20">
-        <v>68.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="G20">
-        <v>65.8</v>
+        <v>72.3</v>
       </c>
       <c r="H20">
-        <v>61</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I20">
-        <v>54.6</v>
+        <v>71</v>
       </c>
       <c r="J20">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="K20">
-        <v>38.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L20">
-        <v>30.3</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1202,37 +1202,37 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>72.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="C21">
-        <v>77.7</v>
+        <v>89.2</v>
       </c>
       <c r="D21">
-        <v>81.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="E21">
-        <v>82.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="F21">
-        <v>81.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G21">
-        <v>77.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H21">
-        <v>71.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I21">
-        <v>63.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J21">
-        <v>54.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K21">
-        <v>44.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L21">
-        <v>34.1</v>
+        <v>85.7</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
@@ -442,37 +442,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46162</v>
+        <v>46197</v>
       </c>
       <c r="C1" s="1">
-        <v>46169</v>
+        <v>46204</v>
       </c>
       <c r="D1" s="1">
-        <v>46176</v>
+        <v>46211</v>
       </c>
       <c r="E1" s="1">
-        <v>46183</v>
+        <v>46218</v>
       </c>
       <c r="F1" s="1">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="G1" s="1">
-        <v>46197</v>
+        <v>46232</v>
       </c>
       <c r="H1" s="1">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="I1" s="1">
-        <v>46211</v>
+        <v>46246</v>
       </c>
       <c r="J1" s="1">
-        <v>46218</v>
+        <v>46253</v>
       </c>
       <c r="K1" s="1">
-        <v>46225</v>
+        <v>46260</v>
       </c>
       <c r="L1" s="1">
-        <v>46232</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -480,37 +480,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>88.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="C2">
-        <v>87.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D2">
-        <v>86.40000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="E2">
-        <v>84.59999999999999</v>
+        <v>51.5</v>
       </c>
       <c r="F2">
-        <v>82.7</v>
+        <v>44.5</v>
       </c>
       <c r="G2">
-        <v>81</v>
+        <v>37.5</v>
       </c>
       <c r="H2">
-        <v>79.90000000000001</v>
+        <v>30.8</v>
       </c>
       <c r="I2">
-        <v>79.5</v>
+        <v>24.5</v>
       </c>
       <c r="J2">
-        <v>79.90000000000001</v>
+        <v>18.7</v>
       </c>
       <c r="K2">
-        <v>81</v>
+        <v>13.4</v>
       </c>
       <c r="L2">
-        <v>82.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -518,37 +518,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>108.5</v>
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>104.5</v>
+        <v>66.7</v>
       </c>
       <c r="D3">
-        <v>99.90000000000001</v>
+        <v>58.5</v>
       </c>
       <c r="E3">
-        <v>95.3</v>
+        <v>50.4</v>
       </c>
       <c r="F3">
-        <v>91</v>
+        <v>42.7</v>
       </c>
       <c r="G3">
-        <v>87.40000000000001</v>
+        <v>35.5</v>
       </c>
       <c r="H3">
-        <v>84.90000000000001</v>
+        <v>28.7</v>
       </c>
       <c r="I3">
-        <v>83.5</v>
+        <v>22.4</v>
       </c>
       <c r="J3">
-        <v>83.2</v>
+        <v>16.8</v>
       </c>
       <c r="K3">
-        <v>83.7</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>84.90000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -556,37 +556,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>78.7</v>
+        <v>53.5</v>
       </c>
       <c r="C4">
-        <v>77.7</v>
+        <v>44.9</v>
       </c>
       <c r="D4">
-        <v>75.59999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="E4">
-        <v>72.8</v>
+        <v>27.7</v>
       </c>
       <c r="F4">
-        <v>69.7</v>
+        <v>19.8</v>
       </c>
       <c r="G4">
-        <v>66.8</v>
+        <v>12.7</v>
       </c>
       <c r="H4">
-        <v>64.59999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>63.5</v>
+        <v>1.6</v>
       </c>
       <c r="J4">
-        <v>63.5</v>
+        <v>-2.3</v>
       </c>
       <c r="K4">
-        <v>64.7</v>
+        <v>-5.1</v>
       </c>
       <c r="L4">
-        <v>67</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -594,37 +594,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>81.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C5">
-        <v>82.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="D5">
-        <v>82.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="E5">
-        <v>81.7</v>
+        <v>60.5</v>
       </c>
       <c r="F5">
-        <v>81</v>
+        <v>54.3</v>
       </c>
       <c r="G5">
-        <v>80.2</v>
+        <v>47.8</v>
       </c>
       <c r="H5">
-        <v>79.40000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="I5">
-        <v>78.7</v>
+        <v>34.8</v>
       </c>
       <c r="J5">
-        <v>78.2</v>
+        <v>28.7</v>
       </c>
       <c r="K5">
-        <v>78</v>
+        <v>23.3</v>
       </c>
       <c r="L5">
-        <v>78.09999999999999</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -632,37 +632,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>100.8</v>
+        <v>80</v>
       </c>
       <c r="C6">
-        <v>99.3</v>
+        <v>73.3</v>
       </c>
       <c r="D6">
-        <v>96.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E6">
-        <v>92.5</v>
+        <v>60.3</v>
       </c>
       <c r="F6">
-        <v>87.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="G6">
-        <v>83.09999999999999</v>
+        <v>49.7</v>
       </c>
       <c r="H6">
-        <v>78.7</v>
+        <v>45.4</v>
       </c>
       <c r="I6">
-        <v>75.09999999999999</v>
+        <v>41.8</v>
       </c>
       <c r="J6">
-        <v>72.5</v>
+        <v>38.5</v>
       </c>
       <c r="K6">
-        <v>71.2</v>
+        <v>35.7</v>
       </c>
       <c r="L6">
-        <v>71</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -670,37 +670,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>101.9</v>
+        <v>87.5</v>
       </c>
       <c r="C7">
-        <v>102.1</v>
+        <v>81.2</v>
       </c>
       <c r="D7">
-        <v>101.4</v>
+        <v>74.5</v>
       </c>
       <c r="E7">
-        <v>100.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F7">
-        <v>99</v>
+        <v>60.5</v>
       </c>
       <c r="G7">
-        <v>98.2</v>
+        <v>53.2</v>
       </c>
       <c r="H7">
-        <v>98.2</v>
+        <v>45.9</v>
       </c>
       <c r="I7">
-        <v>99.3</v>
+        <v>38.4</v>
       </c>
       <c r="J7">
-        <v>101.4</v>
+        <v>30.9</v>
       </c>
       <c r="K7">
-        <v>104.4</v>
+        <v>23.5</v>
       </c>
       <c r="L7">
-        <v>107.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -708,37 +708,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>95.5</v>
+        <v>75.2</v>
       </c>
       <c r="C8">
-        <v>93.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D8">
-        <v>91.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="E8">
-        <v>88.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="F8">
-        <v>86.3</v>
+        <v>47.8</v>
       </c>
       <c r="G8">
-        <v>84</v>
+        <v>41.1</v>
       </c>
       <c r="H8">
-        <v>82.40000000000001</v>
+        <v>34.6</v>
       </c>
       <c r="I8">
-        <v>81.8</v>
+        <v>28.5</v>
       </c>
       <c r="J8">
-        <v>82.09999999999999</v>
+        <v>22.9</v>
       </c>
       <c r="K8">
-        <v>83.3</v>
+        <v>17.8</v>
       </c>
       <c r="L8">
-        <v>85.09999999999999</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -746,37 +746,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>83.5</v>
+        <v>70.7</v>
       </c>
       <c r="C9">
-        <v>84</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D9">
-        <v>83.8</v>
+        <v>57.3</v>
       </c>
       <c r="E9">
-        <v>83.2</v>
+        <v>49.7</v>
       </c>
       <c r="F9">
-        <v>82.40000000000001</v>
+        <v>41.9</v>
       </c>
       <c r="G9">
-        <v>81.59999999999999</v>
+        <v>34.2</v>
       </c>
       <c r="H9">
-        <v>81.09999999999999</v>
+        <v>26.7</v>
       </c>
       <c r="I9">
-        <v>81.09999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="J9">
-        <v>81.8</v>
+        <v>13.5</v>
       </c>
       <c r="K9">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>84.59999999999999</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -784,37 +784,37 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>62.4</v>
+      </c>
+      <c r="C10">
         <v>60.1</v>
       </c>
-      <c r="C10">
-        <v>61.6</v>
-      </c>
       <c r="D10">
-        <v>63.1</v>
+        <v>56.7</v>
       </c>
       <c r="E10">
-        <v>64.7</v>
+        <v>52.1</v>
       </c>
       <c r="F10">
-        <v>66.5</v>
+        <v>46.4</v>
       </c>
       <c r="G10">
-        <v>68.59999999999999</v>
+        <v>39.8</v>
       </c>
       <c r="H10">
-        <v>70.90000000000001</v>
+        <v>32.5</v>
       </c>
       <c r="I10">
-        <v>73.5</v>
+        <v>24.7</v>
       </c>
       <c r="J10">
-        <v>76.2</v>
+        <v>17</v>
       </c>
       <c r="K10">
-        <v>78.90000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L10">
-        <v>81.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -822,37 +822,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>77.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="C11">
-        <v>77.8</v>
+        <v>62.5</v>
       </c>
       <c r="D11">
-        <v>77.7</v>
+        <v>56.4</v>
       </c>
       <c r="E11">
-        <v>77.5</v>
+        <v>49.7</v>
       </c>
       <c r="F11">
-        <v>77.3</v>
+        <v>42.6</v>
       </c>
       <c r="G11">
-        <v>77.2</v>
+        <v>35.3</v>
       </c>
       <c r="H11">
-        <v>77.3</v>
+        <v>28.2</v>
       </c>
       <c r="I11">
-        <v>77.59999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="J11">
-        <v>78.3</v>
+        <v>15.4</v>
       </c>
       <c r="K11">
-        <v>79.40000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="L11">
-        <v>80.59999999999999</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -860,37 +860,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>92.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="C12">
-        <v>89.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="D12">
-        <v>86</v>
+        <v>56.6</v>
       </c>
       <c r="E12">
-        <v>82.40000000000001</v>
+        <v>50.4</v>
       </c>
       <c r="F12">
-        <v>79.09999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="G12">
-        <v>76.40000000000001</v>
+        <v>38.4</v>
       </c>
       <c r="H12">
-        <v>74.8</v>
+        <v>32.7</v>
       </c>
       <c r="I12">
-        <v>74.2</v>
+        <v>27.3</v>
       </c>
       <c r="J12">
-        <v>74.8</v>
+        <v>22.1</v>
       </c>
       <c r="K12">
-        <v>76.3</v>
+        <v>17.4</v>
       </c>
       <c r="L12">
-        <v>78.59999999999999</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -898,37 +898,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>110.8</v>
+        <v>78</v>
       </c>
       <c r="C13">
-        <v>106.9</v>
+        <v>69.5</v>
       </c>
       <c r="D13">
-        <v>102.6</v>
+        <v>60.9</v>
       </c>
       <c r="E13">
-        <v>98.5</v>
+        <v>52.4</v>
       </c>
       <c r="F13">
-        <v>95.09999999999999</v>
+        <v>43.9</v>
       </c>
       <c r="G13">
-        <v>92.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="H13">
-        <v>92.2</v>
+        <v>27.1</v>
       </c>
       <c r="I13">
-        <v>93.09999999999999</v>
+        <v>18.9</v>
       </c>
       <c r="J13">
-        <v>95.40000000000001</v>
+        <v>11</v>
       </c>
       <c r="K13">
-        <v>98.7</v>
+        <v>3.6</v>
       </c>
       <c r="L13">
-        <v>102.7</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -936,37 +936,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>68</v>
+        <v>61.9</v>
       </c>
       <c r="C14">
-        <v>68.59999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="D14">
-        <v>68.40000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="E14">
-        <v>67.5</v>
+        <v>49.8</v>
       </c>
       <c r="F14">
-        <v>66.2</v>
+        <v>45.5</v>
       </c>
       <c r="G14">
-        <v>64.8</v>
+        <v>41.1</v>
       </c>
       <c r="H14">
-        <v>63.7</v>
+        <v>36.9</v>
       </c>
       <c r="I14">
-        <v>62.9</v>
+        <v>32.8</v>
       </c>
       <c r="J14">
-        <v>62.7</v>
+        <v>28.8</v>
       </c>
       <c r="K14">
-        <v>63.2</v>
+        <v>25.1</v>
       </c>
       <c r="L14">
-        <v>64.09999999999999</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -974,37 +974,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C15">
-        <v>85.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="D15">
-        <v>85.3</v>
+        <v>53.8</v>
       </c>
       <c r="E15">
-        <v>84.40000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="F15">
-        <v>83.3</v>
+        <v>37.1</v>
       </c>
       <c r="G15">
-        <v>82.3</v>
+        <v>28.8</v>
       </c>
       <c r="H15">
-        <v>81.7</v>
+        <v>20.8</v>
       </c>
       <c r="I15">
-        <v>81.90000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="J15">
-        <v>82.8</v>
+        <v>6.7</v>
       </c>
       <c r="K15">
-        <v>84.3</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>86.3</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1012,37 +1012,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>101.6</v>
+        <v>75.8</v>
       </c>
       <c r="C16">
-        <v>99.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="D16">
-        <v>97.09999999999999</v>
+        <v>59</v>
       </c>
       <c r="E16">
-        <v>93.59999999999999</v>
+        <v>50.5</v>
       </c>
       <c r="F16">
-        <v>89.8</v>
+        <v>42.5</v>
       </c>
       <c r="G16">
-        <v>86.09999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="H16">
-        <v>83</v>
+        <v>27.9</v>
       </c>
       <c r="I16">
-        <v>80.8</v>
+        <v>21.7</v>
       </c>
       <c r="J16">
-        <v>79.59999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="K16">
-        <v>79.40000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="L16">
-        <v>80</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1050,37 +1050,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>98.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="C17">
-        <v>95.8</v>
+        <v>56.1</v>
       </c>
       <c r="D17">
-        <v>92.8</v>
+        <v>45.6</v>
       </c>
       <c r="E17">
-        <v>89.7</v>
+        <v>34.8</v>
       </c>
       <c r="F17">
-        <v>87.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="G17">
-        <v>85.40000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="H17">
-        <v>85</v>
+        <v>3.5</v>
       </c>
       <c r="I17">
-        <v>86</v>
+        <v>-5.9</v>
       </c>
       <c r="J17">
-        <v>88.2</v>
+        <v>-14.4</v>
       </c>
       <c r="K17">
-        <v>91.59999999999999</v>
+        <v>-21.7</v>
       </c>
       <c r="L17">
-        <v>95.5</v>
+        <v>-27.4</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1088,37 +1088,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>87.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C18">
-        <v>88.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D18">
-        <v>89.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E18">
-        <v>89.2</v>
+        <v>67.2</v>
       </c>
       <c r="F18">
-        <v>87.90000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="G18">
-        <v>85.8</v>
+        <v>56</v>
       </c>
       <c r="H18">
-        <v>83.40000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="I18">
-        <v>80.8</v>
+        <v>46.4</v>
       </c>
       <c r="J18">
-        <v>78.5</v>
+        <v>42.4</v>
       </c>
       <c r="K18">
-        <v>76.59999999999999</v>
+        <v>39</v>
       </c>
       <c r="L18">
-        <v>75.3</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1126,37 +1126,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>85.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="C19">
-        <v>84.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="D19">
-        <v>84.09999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="E19">
-        <v>82.90000000000001</v>
+        <v>51</v>
       </c>
       <c r="F19">
-        <v>81.8</v>
+        <v>44.4</v>
       </c>
       <c r="G19">
-        <v>81.09999999999999</v>
+        <v>37.9</v>
       </c>
       <c r="H19">
-        <v>81.09999999999999</v>
+        <v>31.5</v>
       </c>
       <c r="I19">
-        <v>82.09999999999999</v>
+        <v>25.3</v>
       </c>
       <c r="J19">
-        <v>84</v>
+        <v>19.4</v>
       </c>
       <c r="K19">
-        <v>86.59999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="L19">
-        <v>89.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1164,37 +1164,37 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>74.2</v>
+        <v>67.2</v>
       </c>
       <c r="C20">
-        <v>74.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D20">
-        <v>74.90000000000001</v>
+        <v>57.3</v>
       </c>
       <c r="E20">
-        <v>74.3</v>
+        <v>51.5</v>
       </c>
       <c r="F20">
-        <v>73.3</v>
+        <v>45.3</v>
       </c>
       <c r="G20">
-        <v>72.3</v>
+        <v>39</v>
       </c>
       <c r="H20">
-        <v>71.40000000000001</v>
+        <v>32.8</v>
       </c>
       <c r="I20">
-        <v>71</v>
+        <v>26.7</v>
       </c>
       <c r="J20">
-        <v>71</v>
+        <v>20.8</v>
       </c>
       <c r="K20">
-        <v>71.59999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="L20">
-        <v>72.7</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1202,37 +1202,37 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>88.2</v>
+        <v>75</v>
       </c>
       <c r="C21">
-        <v>89.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="D21">
-        <v>89.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="E21">
-        <v>88.2</v>
+        <v>53.6</v>
       </c>
       <c r="F21">
-        <v>86.90000000000001</v>
+        <v>46.1</v>
       </c>
       <c r="G21">
-        <v>85.40000000000001</v>
+        <v>38.8</v>
       </c>
       <c r="H21">
-        <v>84.2</v>
+        <v>31.9</v>
       </c>
       <c r="I21">
-        <v>83.59999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="J21">
-        <v>83.59999999999999</v>
+        <v>20</v>
       </c>
       <c r="K21">
-        <v>84.40000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="L21">
-        <v>85.7</v>
+        <v>11.2</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
@@ -442,37 +442,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46197</v>
+        <v>46260</v>
       </c>
       <c r="C1" s="1">
-        <v>46204</v>
+        <v>46267</v>
       </c>
       <c r="D1" s="1">
-        <v>46211</v>
+        <v>46274</v>
       </c>
       <c r="E1" s="1">
-        <v>46218</v>
+        <v>46281</v>
       </c>
       <c r="F1" s="1">
-        <v>46225</v>
+        <v>46288</v>
       </c>
       <c r="G1" s="1">
-        <v>46232</v>
+        <v>46295</v>
       </c>
       <c r="H1" s="1">
-        <v>46239</v>
+        <v>46302</v>
       </c>
       <c r="I1" s="1">
-        <v>46246</v>
+        <v>46309</v>
       </c>
       <c r="J1" s="1">
-        <v>46253</v>
+        <v>46316</v>
       </c>
       <c r="K1" s="1">
-        <v>46260</v>
+        <v>46323</v>
       </c>
       <c r="L1" s="1">
-        <v>46267</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -480,37 +480,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>71.7</v>
+        <v>18.9</v>
       </c>
       <c r="C2">
-        <v>65.40000000000001</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>58.6</v>
+        <v>11.9</v>
       </c>
       <c r="E2">
-        <v>51.5</v>
+        <v>9.5</v>
       </c>
       <c r="F2">
-        <v>44.5</v>
+        <v>8.1</v>
       </c>
       <c r="G2">
-        <v>37.5</v>
+        <v>7.7</v>
       </c>
       <c r="H2">
-        <v>30.8</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
-        <v>24.5</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
-        <v>18.7</v>
+        <v>11.5</v>
       </c>
       <c r="K2">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="L2">
-        <v>9.1</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -518,37 +518,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>75</v>
+        <v>7.9</v>
       </c>
       <c r="C3">
-        <v>66.7</v>
+        <v>4.1</v>
       </c>
       <c r="D3">
-        <v>58.5</v>
+        <v>1.2</v>
       </c>
       <c r="E3">
-        <v>50.4</v>
+        <v>-0.6</v>
       </c>
       <c r="F3">
-        <v>42.7</v>
+        <v>-1.6</v>
       </c>
       <c r="G3">
-        <v>35.5</v>
+        <v>-1.7</v>
       </c>
       <c r="H3">
-        <v>28.7</v>
+        <v>-1.2</v>
       </c>
       <c r="I3">
-        <v>22.4</v>
+        <v>-0.3</v>
       </c>
       <c r="J3">
-        <v>16.8</v>
+        <v>0.9</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="L3">
-        <v>8.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -556,37 +556,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>53.5</v>
+        <v>-20.1</v>
       </c>
       <c r="C4">
-        <v>44.9</v>
+        <v>-24.6</v>
       </c>
       <c r="D4">
-        <v>36.2</v>
+        <v>-27.9</v>
       </c>
       <c r="E4">
-        <v>27.7</v>
+        <v>-29.8</v>
       </c>
       <c r="F4">
-        <v>19.8</v>
+        <v>-30.1</v>
       </c>
       <c r="G4">
-        <v>12.7</v>
+        <v>-28.6</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>-25.5</v>
       </c>
       <c r="I4">
-        <v>1.6</v>
+        <v>-20.9</v>
       </c>
       <c r="J4">
-        <v>-2.3</v>
+        <v>-14.9</v>
       </c>
       <c r="K4">
-        <v>-5.1</v>
+        <v>-8</v>
       </c>
       <c r="L4">
-        <v>-6.7</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -594,37 +594,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>75.40000000000001</v>
+        <v>23.1</v>
       </c>
       <c r="C5">
-        <v>71.2</v>
+        <v>18.5</v>
       </c>
       <c r="D5">
-        <v>66.2</v>
+        <v>14.9</v>
       </c>
       <c r="E5">
-        <v>60.5</v>
+        <v>12.3</v>
       </c>
       <c r="F5">
-        <v>54.3</v>
+        <v>10.9</v>
       </c>
       <c r="G5">
-        <v>47.8</v>
+        <v>10.8</v>
       </c>
       <c r="H5">
-        <v>41.2</v>
+        <v>11.8</v>
       </c>
       <c r="I5">
-        <v>34.8</v>
+        <v>13.9</v>
       </c>
       <c r="J5">
-        <v>28.7</v>
+        <v>16.9</v>
       </c>
       <c r="K5">
-        <v>23.3</v>
+        <v>20.6</v>
       </c>
       <c r="L5">
-        <v>18.6</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -632,37 +632,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>80</v>
+        <v>54.9</v>
       </c>
       <c r="C6">
-        <v>73.3</v>
+        <v>56.1</v>
       </c>
       <c r="D6">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="E6">
-        <v>60.3</v>
+        <v>58.1</v>
       </c>
       <c r="F6">
-        <v>54.7</v>
+        <v>58.7</v>
       </c>
       <c r="G6">
-        <v>49.7</v>
+        <v>58.9</v>
       </c>
       <c r="H6">
-        <v>45.4</v>
+        <v>58.9</v>
       </c>
       <c r="I6">
-        <v>41.8</v>
+        <v>58.5</v>
       </c>
       <c r="J6">
-        <v>38.5</v>
+        <v>57.7</v>
       </c>
       <c r="K6">
-        <v>35.7</v>
+        <v>56.7</v>
       </c>
       <c r="L6">
-        <v>33.1</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -670,37 +670,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>87.5</v>
+        <v>50.6</v>
       </c>
       <c r="C7">
-        <v>81.2</v>
+        <v>47.9</v>
       </c>
       <c r="D7">
-        <v>74.5</v>
+        <v>45.3</v>
       </c>
       <c r="E7">
-        <v>67.59999999999999</v>
+        <v>42.8</v>
       </c>
       <c r="F7">
-        <v>60.5</v>
+        <v>40.6</v>
       </c>
       <c r="G7">
-        <v>53.2</v>
+        <v>38.7</v>
       </c>
       <c r="H7">
-        <v>45.9</v>
+        <v>37</v>
       </c>
       <c r="I7">
-        <v>38.4</v>
+        <v>35.6</v>
       </c>
       <c r="J7">
-        <v>30.9</v>
+        <v>34.5</v>
       </c>
       <c r="K7">
-        <v>23.5</v>
+        <v>33.7</v>
       </c>
       <c r="L7">
-        <v>16.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -708,37 +708,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>75.2</v>
+        <v>13.8</v>
       </c>
       <c r="C8">
-        <v>68.59999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="D8">
-        <v>61.6</v>
+        <v>1.2</v>
       </c>
       <c r="E8">
-        <v>54.7</v>
+        <v>-3.5</v>
       </c>
       <c r="F8">
-        <v>47.8</v>
+        <v>-6.9</v>
       </c>
       <c r="G8">
-        <v>41.1</v>
+        <v>-8.6</v>
       </c>
       <c r="H8">
-        <v>34.6</v>
+        <v>-8.6</v>
       </c>
       <c r="I8">
-        <v>28.5</v>
+        <v>-6.8</v>
       </c>
       <c r="J8">
-        <v>22.9</v>
+        <v>-3.4</v>
       </c>
       <c r="K8">
-        <v>17.8</v>
+        <v>1.4</v>
       </c>
       <c r="L8">
-        <v>13.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -746,37 +746,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>70.7</v>
+        <v>16.6</v>
       </c>
       <c r="C9">
-        <v>64.40000000000001</v>
+        <v>13</v>
       </c>
       <c r="D9">
-        <v>57.3</v>
+        <v>10.1</v>
       </c>
       <c r="E9">
-        <v>49.7</v>
+        <v>7.9</v>
       </c>
       <c r="F9">
-        <v>41.9</v>
+        <v>6.5</v>
       </c>
       <c r="G9">
-        <v>34.2</v>
+        <v>5.9</v>
       </c>
       <c r="H9">
-        <v>26.7</v>
+        <v>6.1</v>
       </c>
       <c r="I9">
-        <v>19.7</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>10.6</v>
       </c>
       <c r="L9">
-        <v>3.7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -784,37 +784,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>62.4</v>
+        <v>26.6</v>
       </c>
       <c r="C10">
-        <v>60.1</v>
+        <v>22.2</v>
       </c>
       <c r="D10">
-        <v>56.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10">
-        <v>52.1</v>
+        <v>14.4</v>
       </c>
       <c r="F10">
-        <v>46.4</v>
+        <v>11.1</v>
       </c>
       <c r="G10">
-        <v>39.8</v>
+        <v>8.4</v>
       </c>
       <c r="H10">
-        <v>32.5</v>
+        <v>6.2</v>
       </c>
       <c r="I10">
-        <v>24.7</v>
+        <v>4.7</v>
       </c>
       <c r="J10">
-        <v>17</v>
+        <v>3.8</v>
       </c>
       <c r="K10">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
-        <v>3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -822,37 +822,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>67.59999999999999</v>
+        <v>20.1</v>
       </c>
       <c r="C11">
-        <v>62.5</v>
+        <v>15.4</v>
       </c>
       <c r="D11">
-        <v>56.4</v>
+        <v>11.2</v>
       </c>
       <c r="E11">
-        <v>49.7</v>
+        <v>7.7</v>
       </c>
       <c r="F11">
-        <v>42.6</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>35.3</v>
+        <v>3.2</v>
       </c>
       <c r="H11">
-        <v>28.2</v>
+        <v>2.4</v>
       </c>
       <c r="I11">
-        <v>21.5</v>
+        <v>2.6</v>
       </c>
       <c r="J11">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
-        <v>10.3</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>6.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -860,37 +860,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>69.09999999999999</v>
+        <v>19</v>
       </c>
       <c r="C12">
-        <v>62.9</v>
+        <v>14.9</v>
       </c>
       <c r="D12">
-        <v>56.6</v>
+        <v>11.4</v>
       </c>
       <c r="E12">
-        <v>50.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F12">
-        <v>44.3</v>
+        <v>7.1</v>
       </c>
       <c r="G12">
-        <v>38.4</v>
+        <v>6.4</v>
       </c>
       <c r="H12">
-        <v>32.7</v>
+        <v>6.8</v>
       </c>
       <c r="I12">
-        <v>27.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
-        <v>22.1</v>
+        <v>10.4</v>
       </c>
       <c r="K12">
-        <v>17.4</v>
+        <v>13.4</v>
       </c>
       <c r="L12">
-        <v>13.3</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -898,37 +898,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>78</v>
+        <v>12.9</v>
       </c>
       <c r="C13">
-        <v>69.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D13">
-        <v>60.9</v>
+        <v>7.1</v>
       </c>
       <c r="E13">
-        <v>52.4</v>
+        <v>6.5</v>
       </c>
       <c r="F13">
-        <v>43.9</v>
+        <v>7.4</v>
       </c>
       <c r="G13">
-        <v>35.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H13">
-        <v>27.1</v>
+        <v>13.5</v>
       </c>
       <c r="I13">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="J13">
-        <v>11</v>
+        <v>23.4</v>
       </c>
       <c r="K13">
-        <v>3.6</v>
+        <v>28.7</v>
       </c>
       <c r="L13">
-        <v>-2.8</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -936,37 +936,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>61.9</v>
+        <v>34</v>
       </c>
       <c r="C14">
-        <v>58.2</v>
+        <v>31.6</v>
       </c>
       <c r="D14">
-        <v>54.1</v>
+        <v>29.4</v>
       </c>
       <c r="E14">
-        <v>49.8</v>
+        <v>27.3</v>
       </c>
       <c r="F14">
-        <v>45.5</v>
+        <v>25.4</v>
       </c>
       <c r="G14">
-        <v>41.1</v>
+        <v>23.9</v>
       </c>
       <c r="H14">
-        <v>36.9</v>
+        <v>22.7</v>
       </c>
       <c r="I14">
-        <v>32.8</v>
+        <v>22</v>
       </c>
       <c r="J14">
-        <v>28.8</v>
+        <v>21.6</v>
       </c>
       <c r="K14">
-        <v>25.1</v>
+        <v>21.7</v>
       </c>
       <c r="L14">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -974,37 +974,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>69</v>
+        <v>11.4</v>
       </c>
       <c r="C15">
-        <v>61.8</v>
+        <v>6.9</v>
       </c>
       <c r="D15">
-        <v>53.8</v>
+        <v>3.2</v>
       </c>
       <c r="E15">
-        <v>45.5</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
-        <v>37.1</v>
+        <v>-1.1</v>
       </c>
       <c r="G15">
-        <v>28.8</v>
+        <v>-1.5</v>
       </c>
       <c r="H15">
-        <v>20.8</v>
+        <v>-0.9</v>
       </c>
       <c r="I15">
-        <v>13.4</v>
+        <v>0.9</v>
       </c>
       <c r="J15">
-        <v>6.7</v>
+        <v>3.5</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-3.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1012,37 +1012,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>75.8</v>
+        <v>-1</v>
       </c>
       <c r="C16">
-        <v>67.5</v>
+        <v>-5.2</v>
       </c>
       <c r="D16">
-        <v>59</v>
+        <v>-7.7</v>
       </c>
       <c r="E16">
-        <v>50.5</v>
+        <v>-8.5</v>
       </c>
       <c r="F16">
-        <v>42.5</v>
+        <v>-7.6</v>
       </c>
       <c r="G16">
-        <v>34.9</v>
+        <v>-5</v>
       </c>
       <c r="H16">
-        <v>27.9</v>
+        <v>-1.1</v>
       </c>
       <c r="I16">
-        <v>21.7</v>
+        <v>4</v>
       </c>
       <c r="J16">
-        <v>16.2</v>
+        <v>9.9</v>
       </c>
       <c r="K16">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="L16">
-        <v>7.9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1050,37 +1050,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>66.09999999999999</v>
+        <v>-4.8</v>
       </c>
       <c r="C17">
-        <v>56.1</v>
+        <v>-7.5</v>
       </c>
       <c r="D17">
-        <v>45.6</v>
+        <v>-8.5</v>
       </c>
       <c r="E17">
-        <v>34.8</v>
+        <v>-7.9</v>
       </c>
       <c r="F17">
-        <v>24.1</v>
+        <v>-5.5</v>
       </c>
       <c r="G17">
-        <v>13.6</v>
+        <v>-1.8</v>
       </c>
       <c r="H17">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>-5.9</v>
+        <v>8.6</v>
       </c>
       <c r="J17">
-        <v>-14.4</v>
+        <v>14.4</v>
       </c>
       <c r="K17">
-        <v>-21.7</v>
+        <v>20.1</v>
       </c>
       <c r="L17">
-        <v>-27.4</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1088,37 +1088,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>82.7</v>
+        <v>19</v>
       </c>
       <c r="C18">
-        <v>78.09999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="D18">
-        <v>72.8</v>
+        <v>5.1</v>
       </c>
       <c r="E18">
-        <v>67.2</v>
+        <v>-0.6</v>
       </c>
       <c r="F18">
-        <v>61.5</v>
+        <v>-4.9</v>
       </c>
       <c r="G18">
-        <v>56</v>
+        <v>-7.8</v>
       </c>
       <c r="H18">
-        <v>50.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I18">
-        <v>46.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="J18">
-        <v>42.4</v>
+        <v>-6.9</v>
       </c>
       <c r="K18">
-        <v>39</v>
+        <v>-3.5</v>
       </c>
       <c r="L18">
-        <v>36.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1126,37 +1126,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>69.8</v>
+        <v>33.3</v>
       </c>
       <c r="C19">
-        <v>63.9</v>
+        <v>31.1</v>
       </c>
       <c r="D19">
-        <v>57.5</v>
+        <v>29.1</v>
       </c>
       <c r="E19">
-        <v>51</v>
+        <v>27.4</v>
       </c>
       <c r="F19">
-        <v>44.4</v>
+        <v>25.9</v>
       </c>
       <c r="G19">
-        <v>37.9</v>
+        <v>24.8</v>
       </c>
       <c r="H19">
-        <v>31.5</v>
+        <v>24</v>
       </c>
       <c r="I19">
-        <v>25.3</v>
+        <v>23.5</v>
       </c>
       <c r="J19">
-        <v>19.4</v>
+        <v>23.3</v>
       </c>
       <c r="K19">
-        <v>13.9</v>
+        <v>23.4</v>
       </c>
       <c r="L19">
-        <v>9</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1164,37 +1164,37 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>67.2</v>
+        <v>28.6</v>
       </c>
       <c r="C20">
-        <v>62.6</v>
+        <v>25.1</v>
       </c>
       <c r="D20">
-        <v>57.3</v>
+        <v>22</v>
       </c>
       <c r="E20">
-        <v>51.5</v>
+        <v>19.2</v>
       </c>
       <c r="F20">
-        <v>45.3</v>
+        <v>16.9</v>
       </c>
       <c r="G20">
-        <v>39</v>
+        <v>15.2</v>
       </c>
       <c r="H20">
-        <v>32.8</v>
+        <v>14.1</v>
       </c>
       <c r="I20">
-        <v>26.7</v>
+        <v>13.7</v>
       </c>
       <c r="J20">
-        <v>20.8</v>
+        <v>13.8</v>
       </c>
       <c r="K20">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="L20">
-        <v>10.8</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1202,37 +1202,37 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>75</v>
+        <v>13.2</v>
       </c>
       <c r="C21">
-        <v>68.40000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="D21">
-        <v>61.1</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>53.6</v>
+        <v>-0.9</v>
       </c>
       <c r="F21">
-        <v>46.1</v>
+        <v>-3.8</v>
       </c>
       <c r="G21">
-        <v>38.8</v>
+        <v>-5.6</v>
       </c>
       <c r="H21">
-        <v>31.9</v>
+        <v>-6</v>
       </c>
       <c r="I21">
-        <v>25.6</v>
+        <v>-5.2</v>
       </c>
       <c r="J21">
-        <v>20</v>
+        <v>-3.2</v>
       </c>
       <c r="K21">
-        <v>15.1</v>
+        <v>-0.1</v>
       </c>
       <c r="L21">
-        <v>11.2</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_1/VCI3M_Forecast_Overview_CLUSTER_1.xlsx
@@ -442,37 +442,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46260</v>
+        <v>46281</v>
       </c>
       <c r="C1" s="1">
-        <v>46267</v>
+        <v>46288</v>
       </c>
       <c r="D1" s="1">
-        <v>46274</v>
+        <v>46295</v>
       </c>
       <c r="E1" s="1">
-        <v>46281</v>
+        <v>46302</v>
       </c>
       <c r="F1" s="1">
-        <v>46288</v>
+        <v>46309</v>
       </c>
       <c r="G1" s="1">
-        <v>46295</v>
+        <v>46316</v>
       </c>
       <c r="H1" s="1">
-        <v>46302</v>
+        <v>46323</v>
       </c>
       <c r="I1" s="1">
-        <v>46309</v>
+        <v>46330</v>
       </c>
       <c r="J1" s="1">
-        <v>46316</v>
+        <v>46337</v>
       </c>
       <c r="K1" s="1">
-        <v>46323</v>
+        <v>46344</v>
       </c>
       <c r="L1" s="1">
-        <v>46330</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -480,37 +480,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>18.9</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>3.3</v>
       </c>
       <c r="D2">
-        <v>11.9</v>
+        <v>0.3</v>
       </c>
       <c r="E2">
-        <v>9.5</v>
+        <v>-2.3</v>
       </c>
       <c r="F2">
-        <v>8.1</v>
+        <v>-4.4</v>
       </c>
       <c r="G2">
-        <v>7.7</v>
+        <v>-6.1</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>-7.4</v>
       </c>
       <c r="I2">
-        <v>9.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>11.5</v>
+        <v>-8.4</v>
       </c>
       <c r="K2">
-        <v>14.1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L2">
-        <v>17.1</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -518,37 +518,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>7.9</v>
+        <v>-5.2</v>
       </c>
       <c r="C3">
-        <v>4.1</v>
+        <v>-9.6</v>
       </c>
       <c r="D3">
-        <v>1.2</v>
+        <v>-14.2</v>
       </c>
       <c r="E3">
-        <v>-0.6</v>
+        <v>-19.3</v>
       </c>
       <c r="F3">
-        <v>-1.6</v>
+        <v>-24.7</v>
       </c>
       <c r="G3">
-        <v>-1.7</v>
+        <v>-30.5</v>
       </c>
       <c r="H3">
-        <v>-1.2</v>
+        <v>-36.5</v>
       </c>
       <c r="I3">
-        <v>-0.3</v>
+        <v>-42.4</v>
       </c>
       <c r="J3">
-        <v>0.9</v>
+        <v>-47.8</v>
       </c>
       <c r="K3">
-        <v>2.1</v>
+        <v>-52.3</v>
       </c>
       <c r="L3">
-        <v>3.4</v>
+        <v>-55.4</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -556,37 +556,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>-20.1</v>
+        <v>-32.7</v>
       </c>
       <c r="C4">
-        <v>-24.6</v>
+        <v>-35.2</v>
       </c>
       <c r="D4">
-        <v>-27.9</v>
+        <v>-36.6</v>
       </c>
       <c r="E4">
-        <v>-29.8</v>
+        <v>-36.9</v>
       </c>
       <c r="F4">
-        <v>-30.1</v>
+        <v>-36.3</v>
       </c>
       <c r="G4">
-        <v>-28.6</v>
+        <v>-34.7</v>
       </c>
       <c r="H4">
-        <v>-25.5</v>
+        <v>-32.3</v>
       </c>
       <c r="I4">
-        <v>-20.9</v>
+        <v>-29.3</v>
       </c>
       <c r="J4">
-        <v>-14.9</v>
+        <v>-25.8</v>
       </c>
       <c r="K4">
-        <v>-8</v>
+        <v>-21.9</v>
       </c>
       <c r="L4">
-        <v>-0.5</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -594,37 +594,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>23.1</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>18.5</v>
+        <v>1.9</v>
       </c>
       <c r="D5">
-        <v>14.9</v>
+        <v>-3.2</v>
       </c>
       <c r="E5">
-        <v>12.3</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F5">
-        <v>10.9</v>
+        <v>-13</v>
       </c>
       <c r="G5">
-        <v>10.8</v>
+        <v>-17.6</v>
       </c>
       <c r="H5">
-        <v>11.8</v>
+        <v>-21.9</v>
       </c>
       <c r="I5">
-        <v>13.9</v>
+        <v>-25.7</v>
       </c>
       <c r="J5">
-        <v>16.9</v>
+        <v>-28.7</v>
       </c>
       <c r="K5">
-        <v>20.6</v>
+        <v>-30.9</v>
       </c>
       <c r="L5">
-        <v>24.6</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -632,37 +632,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>54.9</v>
+        <v>58.4</v>
       </c>
       <c r="C6">
-        <v>56.1</v>
+        <v>59.2</v>
       </c>
       <c r="D6">
-        <v>57.2</v>
+        <v>59.9</v>
       </c>
       <c r="E6">
-        <v>58.1</v>
+        <v>60.3</v>
       </c>
       <c r="F6">
-        <v>58.7</v>
+        <v>60.5</v>
       </c>
       <c r="G6">
-        <v>58.9</v>
+        <v>60.4</v>
       </c>
       <c r="H6">
-        <v>58.9</v>
+        <v>60</v>
       </c>
       <c r="I6">
-        <v>58.5</v>
+        <v>59.4</v>
       </c>
       <c r="J6">
-        <v>57.7</v>
+        <v>58.6</v>
       </c>
       <c r="K6">
-        <v>56.7</v>
+        <v>57.6</v>
       </c>
       <c r="L6">
-        <v>55.4</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -670,37 +670,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>50.6</v>
+        <v>41.8</v>
       </c>
       <c r="C7">
-        <v>47.9</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>45.3</v>
+        <v>36.3</v>
       </c>
       <c r="E7">
-        <v>42.8</v>
+        <v>33.8</v>
       </c>
       <c r="F7">
-        <v>40.6</v>
+        <v>31.5</v>
       </c>
       <c r="G7">
-        <v>38.7</v>
+        <v>29.5</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>27.7</v>
       </c>
       <c r="I7">
-        <v>35.6</v>
+        <v>26.2</v>
       </c>
       <c r="J7">
-        <v>34.5</v>
+        <v>24.9</v>
       </c>
       <c r="K7">
-        <v>33.7</v>
+        <v>24</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -708,37 +708,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>13.8</v>
+        <v>-5</v>
       </c>
       <c r="C8">
-        <v>7.1</v>
+        <v>-9.6</v>
       </c>
       <c r="D8">
-        <v>1.2</v>
+        <v>-13</v>
       </c>
       <c r="E8">
-        <v>-3.5</v>
+        <v>-15</v>
       </c>
       <c r="F8">
-        <v>-6.9</v>
+        <v>-15.5</v>
       </c>
       <c r="G8">
-        <v>-8.6</v>
+        <v>-14.7</v>
       </c>
       <c r="H8">
-        <v>-8.6</v>
+        <v>-12.8</v>
       </c>
       <c r="I8">
-        <v>-6.8</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="J8">
-        <v>-3.4</v>
+        <v>-6</v>
       </c>
       <c r="K8">
-        <v>1.4</v>
+        <v>-1.7</v>
       </c>
       <c r="L8">
-        <v>7.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -746,37 +746,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>16.6</v>
+        <v>4.1</v>
       </c>
       <c r="C9">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>10.1</v>
+        <v>-2.8</v>
       </c>
       <c r="E9">
-        <v>7.9</v>
+        <v>-5.8</v>
       </c>
       <c r="F9">
-        <v>6.5</v>
+        <v>-8.4</v>
       </c>
       <c r="G9">
-        <v>5.9</v>
+        <v>-10.5</v>
       </c>
       <c r="H9">
-        <v>6.1</v>
+        <v>-12.1</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>-13.1</v>
       </c>
       <c r="J9">
-        <v>8.5</v>
+        <v>-13.4</v>
       </c>
       <c r="K9">
-        <v>10.6</v>
+        <v>-12.9</v>
       </c>
       <c r="L9">
-        <v>13</v>
+        <v>-11.6</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -784,37 +784,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>26.6</v>
+        <v>9.5</v>
       </c>
       <c r="C10">
-        <v>22.2</v>
+        <v>3.3</v>
       </c>
       <c r="D10">
-        <v>18.1</v>
+        <v>-3.1</v>
       </c>
       <c r="E10">
-        <v>14.4</v>
+        <v>-9.4</v>
       </c>
       <c r="F10">
-        <v>11.1</v>
+        <v>-15.6</v>
       </c>
       <c r="G10">
-        <v>8.4</v>
+        <v>-21.3</v>
       </c>
       <c r="H10">
-        <v>6.2</v>
+        <v>-26.4</v>
       </c>
       <c r="I10">
-        <v>4.7</v>
+        <v>-30.6</v>
       </c>
       <c r="J10">
-        <v>3.8</v>
+        <v>-33.6</v>
       </c>
       <c r="K10">
-        <v>3.6</v>
+        <v>-35.4</v>
       </c>
       <c r="L10">
-        <v>3.9</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -822,37 +822,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>20.1</v>
+        <v>4.6</v>
       </c>
       <c r="C11">
-        <v>15.4</v>
+        <v>-0</v>
       </c>
       <c r="D11">
-        <v>11.2</v>
+        <v>-4.3</v>
       </c>
       <c r="E11">
-        <v>7.7</v>
+        <v>-8</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>-10.9</v>
       </c>
       <c r="G11">
-        <v>3.2</v>
+        <v>-13.1</v>
       </c>
       <c r="H11">
-        <v>2.4</v>
+        <v>-14.3</v>
       </c>
       <c r="I11">
-        <v>2.6</v>
+        <v>-14.6</v>
       </c>
       <c r="J11">
-        <v>3.8</v>
+        <v>-13.8</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>-12.1</v>
       </c>
       <c r="L11">
-        <v>9</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -860,37 +860,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>14.9</v>
+        <v>0.6</v>
       </c>
       <c r="D12">
-        <v>11.4</v>
+        <v>-3.6</v>
       </c>
       <c r="E12">
-        <v>8.800000000000001</v>
+        <v>-7.5</v>
       </c>
       <c r="F12">
-        <v>7.1</v>
+        <v>-11</v>
       </c>
       <c r="G12">
-        <v>6.4</v>
+        <v>-14.1</v>
       </c>
       <c r="H12">
-        <v>6.8</v>
+        <v>-16.6</v>
       </c>
       <c r="I12">
-        <v>8.199999999999999</v>
+        <v>-18.6</v>
       </c>
       <c r="J12">
-        <v>10.4</v>
+        <v>-19.8</v>
       </c>
       <c r="K12">
-        <v>13.4</v>
+        <v>-20.3</v>
       </c>
       <c r="L12">
-        <v>16.9</v>
+        <v>-19.9</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -898,37 +898,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>12.9</v>
+        <v>-0.6</v>
       </c>
       <c r="C13">
-        <v>9.300000000000001</v>
+        <v>-4.5</v>
       </c>
       <c r="D13">
-        <v>7.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="E13">
-        <v>6.5</v>
+        <v>-12.1</v>
       </c>
       <c r="F13">
-        <v>7.4</v>
+        <v>-15.9</v>
       </c>
       <c r="G13">
-        <v>9.800000000000001</v>
+        <v>-19.9</v>
       </c>
       <c r="H13">
-        <v>13.5</v>
+        <v>-24</v>
       </c>
       <c r="I13">
-        <v>18.2</v>
+        <v>-28.1</v>
       </c>
       <c r="J13">
-        <v>23.4</v>
+        <v>-32</v>
       </c>
       <c r="K13">
-        <v>28.7</v>
+        <v>-35.5</v>
       </c>
       <c r="L13">
-        <v>33.8</v>
+        <v>-38.1</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -936,37 +936,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>34</v>
+        <v>27.1</v>
       </c>
       <c r="C14">
-        <v>31.6</v>
+        <v>25.1</v>
       </c>
       <c r="D14">
-        <v>29.4</v>
+        <v>23.4</v>
       </c>
       <c r="E14">
-        <v>27.3</v>
+        <v>22.1</v>
       </c>
       <c r="F14">
-        <v>25.4</v>
+        <v>21.1</v>
       </c>
       <c r="G14">
-        <v>23.9</v>
+        <v>20.6</v>
       </c>
       <c r="H14">
-        <v>22.7</v>
+        <v>20.5</v>
       </c>
       <c r="I14">
-        <v>22</v>
+        <v>20.7</v>
       </c>
       <c r="J14">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="K14">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="L14">
-        <v>22.1</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -974,37 +974,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>11.4</v>
+        <v>-0.5</v>
       </c>
       <c r="C15">
-        <v>6.9</v>
+        <v>-2.9</v>
       </c>
       <c r="D15">
-        <v>3.2</v>
+        <v>-4.4</v>
       </c>
       <c r="E15">
-        <v>0.5</v>
+        <v>-5</v>
       </c>
       <c r="F15">
-        <v>-1.1</v>
+        <v>-4.8</v>
       </c>
       <c r="G15">
-        <v>-1.5</v>
+        <v>-3.8</v>
       </c>
       <c r="H15">
-        <v>-0.9</v>
+        <v>-2.2</v>
       </c>
       <c r="I15">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="K15">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="L15">
-        <v>10.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1012,37 +1012,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>-14.6</v>
       </c>
       <c r="C16">
-        <v>-5.2</v>
+        <v>-17.8</v>
       </c>
       <c r="D16">
-        <v>-7.7</v>
+        <v>-20.6</v>
       </c>
       <c r="E16">
-        <v>-8.5</v>
+        <v>-23.1</v>
       </c>
       <c r="F16">
-        <v>-7.6</v>
+        <v>-25.4</v>
       </c>
       <c r="G16">
-        <v>-5</v>
+        <v>-27.5</v>
       </c>
       <c r="H16">
-        <v>-1.1</v>
+        <v>-29.6</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>-31.6</v>
       </c>
       <c r="J16">
-        <v>9.9</v>
+        <v>-33.4</v>
       </c>
       <c r="K16">
-        <v>16</v>
+        <v>-34.8</v>
       </c>
       <c r="L16">
-        <v>22</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1050,37 +1050,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>-4.8</v>
+        <v>-13.5</v>
       </c>
       <c r="C17">
-        <v>-7.5</v>
+        <v>-15.1</v>
       </c>
       <c r="D17">
-        <v>-8.5</v>
+        <v>-16.2</v>
       </c>
       <c r="E17">
-        <v>-7.9</v>
+        <v>-17.3</v>
       </c>
       <c r="F17">
-        <v>-5.5</v>
+        <v>-18.4</v>
       </c>
       <c r="G17">
-        <v>-1.8</v>
+        <v>-19.8</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>-21.5</v>
       </c>
       <c r="I17">
-        <v>8.6</v>
+        <v>-23.5</v>
       </c>
       <c r="J17">
-        <v>14.4</v>
+        <v>-25.7</v>
       </c>
       <c r="K17">
-        <v>20.1</v>
+        <v>-27.6</v>
       </c>
       <c r="L17">
-        <v>25.4</v>
+        <v>-29.1</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1088,37 +1088,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>19</v>
+        <v>-1.5</v>
       </c>
       <c r="C18">
-        <v>11.7</v>
+        <v>-6.9</v>
       </c>
       <c r="D18">
-        <v>5.1</v>
+        <v>-11.3</v>
       </c>
       <c r="E18">
-        <v>-0.6</v>
+        <v>-14.4</v>
       </c>
       <c r="F18">
-        <v>-4.9</v>
+        <v>-16.2</v>
       </c>
       <c r="G18">
-        <v>-7.8</v>
+        <v>-16.7</v>
       </c>
       <c r="H18">
-        <v>-9.199999999999999</v>
+        <v>-16</v>
       </c>
       <c r="I18">
-        <v>-8.800000000000001</v>
+        <v>-14.2</v>
       </c>
       <c r="J18">
-        <v>-6.9</v>
+        <v>-11.4</v>
       </c>
       <c r="K18">
-        <v>-3.5</v>
+        <v>-7.9</v>
       </c>
       <c r="L18">
-        <v>1.1</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1126,37 +1126,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>33.3</v>
+        <v>26.8</v>
       </c>
       <c r="C19">
-        <v>31.1</v>
+        <v>25</v>
       </c>
       <c r="D19">
-        <v>29.1</v>
+        <v>23.4</v>
       </c>
       <c r="E19">
-        <v>27.4</v>
+        <v>22.2</v>
       </c>
       <c r="F19">
-        <v>25.9</v>
+        <v>21.3</v>
       </c>
       <c r="G19">
-        <v>24.8</v>
+        <v>20.6</v>
       </c>
       <c r="H19">
-        <v>24</v>
+        <v>20.3</v>
       </c>
       <c r="I19">
-        <v>23.5</v>
+        <v>20.2</v>
       </c>
       <c r="J19">
-        <v>23.3</v>
+        <v>20.4</v>
       </c>
       <c r="K19">
-        <v>23.4</v>
+        <v>20.8</v>
       </c>
       <c r="L19">
-        <v>23.7</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1164,37 +1164,37 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>28.6</v>
+        <v>18.3</v>
       </c>
       <c r="C20">
-        <v>25.1</v>
+        <v>15.5</v>
       </c>
       <c r="D20">
-        <v>22</v>
+        <v>13.1</v>
       </c>
       <c r="E20">
-        <v>19.2</v>
+        <v>11.2</v>
       </c>
       <c r="F20">
-        <v>16.9</v>
+        <v>9.9</v>
       </c>
       <c r="G20">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H20">
-        <v>14.1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>13.7</v>
+        <v>9.4</v>
       </c>
       <c r="J20">
-        <v>13.8</v>
+        <v>10.2</v>
       </c>
       <c r="K20">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="L20">
-        <v>15.7</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1202,37 +1202,37 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>13.2</v>
+        <v>-2.2</v>
       </c>
       <c r="C21">
-        <v>7.8</v>
+        <v>-6.1</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>-9.1</v>
       </c>
       <c r="E21">
-        <v>-0.9</v>
+        <v>-11.1</v>
       </c>
       <c r="F21">
-        <v>-3.8</v>
+        <v>-12.1</v>
       </c>
       <c r="G21">
-        <v>-5.6</v>
+        <v>-12</v>
       </c>
       <c r="H21">
-        <v>-6</v>
+        <v>-11.1</v>
       </c>
       <c r="I21">
-        <v>-5.2</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J21">
-        <v>-3.2</v>
+        <v>-6.8</v>
       </c>
       <c r="K21">
-        <v>-0.1</v>
+        <v>-3.7</v>
       </c>
       <c r="L21">
-        <v>3.8</v>
+        <v>-0.2</v>
       </c>
     </row>
   </sheetData>
